--- a/reponsevie/lambda_scan/lambda_0.10/MSD_H.xlsx
+++ b/reponsevie/lambda_scan/lambda_0.10/MSD_H.xlsx
@@ -1,29 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\2A\TP modelisation\modelisation-2A\reponsevie\lambda_scan\lambda_0.10\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0067A5-340E-4BB6-8244-FDCC9C0BF325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="1185" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>run_1</t>
+  </si>
+  <si>
+    <t>run_2</t>
+  </si>
+  <si>
+    <t>run_3</t>
+  </si>
+  <si>
+    <t>run_4</t>
+  </si>
+  <si>
+    <t>run_5</t>
+  </si>
+  <si>
+    <t>run_moy</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,6 +116,1101 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>run_moy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.6250656167979003E-2"/>
+                  <c:y val="0.19633566637503647"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$G$2:$G$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2.3113327999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7053932000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9504426000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.1720244000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3839267999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5075308000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.6612678000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.7297739999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.8521354000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.9209647999999993</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.069693</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.1683043999999994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1462327999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.1654287999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.2438698000000006</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.2522205999999994</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.2398932</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.3300651999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.3988320000000005</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.5678858</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.6186130000000007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.7420265999999991</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.7914623999999995</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.8414701999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.0987604000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1CC1-4671-9E31-7C0E8DA1F56A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1824946815"/>
+        <c:axId val="1824950143"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1824946815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1824950143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1824950143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1824946815"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14DE9A7F-E50D-4044-B252-3734B7E10AE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1475,636 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.5</v>
+      </c>
+      <c r="B2">
+        <v>2.0545629999999999</v>
+      </c>
+      <c r="C2">
+        <v>1.582085</v>
+      </c>
+      <c r="D2">
+        <v>2.618204</v>
+      </c>
+      <c r="E2">
+        <v>2.5626500000000001</v>
+      </c>
+      <c r="F2">
+        <v>2.7391619999999999</v>
+      </c>
+      <c r="G2">
+        <f>AVERAGE(B2:F2)</f>
+        <v>2.3113327999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2.5685389999999999</v>
+      </c>
+      <c r="C3">
+        <v>2.1538810000000002</v>
+      </c>
+      <c r="D3">
+        <v>2.808503</v>
+      </c>
+      <c r="E3">
+        <v>2.8524539999999998</v>
+      </c>
+      <c r="F3">
+        <v>3.143589</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G26" si="0">AVERAGE(B3:F3)</f>
+        <v>2.7053932000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1.5</v>
+      </c>
+      <c r="B4">
+        <v>3.1868720000000001</v>
+      </c>
+      <c r="C4">
+        <v>2.2286109999999999</v>
+      </c>
+      <c r="D4">
+        <v>3.1644830000000002</v>
+      </c>
+      <c r="E4">
+        <v>3.03261</v>
+      </c>
+      <c r="F4">
+        <v>3.139637</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>2.9504426000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>3.5024169999999999</v>
+      </c>
+      <c r="C5">
+        <v>2.360563</v>
+      </c>
+      <c r="D5">
+        <v>3.5251670000000002</v>
+      </c>
+      <c r="E5">
+        <v>3.2888540000000002</v>
+      </c>
+      <c r="F5">
+        <v>3.1831209999999999</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>3.1720244000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2.5</v>
+      </c>
+      <c r="B6">
+        <v>3.772303</v>
+      </c>
+      <c r="C6">
+        <v>2.4427919999999999</v>
+      </c>
+      <c r="D6">
+        <v>3.6685270000000001</v>
+      </c>
+      <c r="E6">
+        <v>3.5037349999999998</v>
+      </c>
+      <c r="F6">
+        <v>3.5322770000000001</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>3.3839267999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>3.9769990000000002</v>
+      </c>
+      <c r="C7">
+        <v>2.5070800000000002</v>
+      </c>
+      <c r="D7">
+        <v>3.7750050000000002</v>
+      </c>
+      <c r="E7">
+        <v>3.5998570000000001</v>
+      </c>
+      <c r="F7">
+        <v>3.6787130000000001</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>3.5075308000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3.5</v>
+      </c>
+      <c r="B8">
+        <v>4.2263080000000004</v>
+      </c>
+      <c r="C8">
+        <v>2.7131750000000001</v>
+      </c>
+      <c r="D8">
+        <v>3.8764259999999999</v>
+      </c>
+      <c r="E8">
+        <v>3.7703479999999998</v>
+      </c>
+      <c r="F8">
+        <v>3.7200820000000001</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>3.6612678000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>4.3695880000000002</v>
+      </c>
+      <c r="C9">
+        <v>2.949319</v>
+      </c>
+      <c r="D9">
+        <v>3.9828009999999998</v>
+      </c>
+      <c r="E9">
+        <v>3.7675649999999998</v>
+      </c>
+      <c r="F9">
+        <v>3.5795970000000001</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>3.7297739999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4.5</v>
+      </c>
+      <c r="B10">
+        <v>4.518338</v>
+      </c>
+      <c r="C10">
+        <v>3.1768779999999999</v>
+      </c>
+      <c r="D10">
+        <v>4.007987</v>
+      </c>
+      <c r="E10">
+        <v>3.976912</v>
+      </c>
+      <c r="F10">
+        <v>3.580562</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>3.8521354000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>4.6931370000000001</v>
+      </c>
+      <c r="C11">
+        <v>3.418885</v>
+      </c>
+      <c r="D11">
+        <v>3.8911310000000001</v>
+      </c>
+      <c r="E11">
+        <v>3.9751029999999998</v>
+      </c>
+      <c r="F11">
+        <v>3.6265679999999998</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>3.9209647999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>5.5</v>
+      </c>
+      <c r="B12">
+        <v>4.7149890000000001</v>
+      </c>
+      <c r="C12">
+        <v>3.6514129999999998</v>
+      </c>
+      <c r="D12">
+        <v>3.8778809999999999</v>
+      </c>
+      <c r="E12">
+        <v>4.2173489999999996</v>
+      </c>
+      <c r="F12">
+        <v>3.8868330000000002</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>4.069693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>4.7654139999999998</v>
+      </c>
+      <c r="C13">
+        <v>3.762769</v>
+      </c>
+      <c r="D13">
+        <v>4.051552</v>
+      </c>
+      <c r="E13">
+        <v>4.5282600000000004</v>
+      </c>
+      <c r="F13">
+        <v>3.733527</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>4.1683043999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6.5</v>
+      </c>
+      <c r="B14">
+        <v>4.6948109999999996</v>
+      </c>
+      <c r="C14">
+        <v>3.93154</v>
+      </c>
+      <c r="D14">
+        <v>3.8753190000000002</v>
+      </c>
+      <c r="E14">
+        <v>4.6898330000000001</v>
+      </c>
+      <c r="F14">
+        <v>3.5396610000000002</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>4.1462327999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>4.6734790000000004</v>
+      </c>
+      <c r="C15">
+        <v>3.9875349999999998</v>
+      </c>
+      <c r="D15">
+        <v>4.065086</v>
+      </c>
+      <c r="E15">
+        <v>4.7472909999999997</v>
+      </c>
+      <c r="F15">
+        <v>3.3537530000000002</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>4.1654287999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7.5</v>
+      </c>
+      <c r="B16">
+        <v>4.7250310000000004</v>
+      </c>
+      <c r="C16">
+        <v>3.8707539999999998</v>
+      </c>
+      <c r="D16">
+        <v>3.9749530000000002</v>
+      </c>
+      <c r="E16">
+        <v>5.1078910000000004</v>
+      </c>
+      <c r="F16">
+        <v>3.5407199999999999</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>4.2438698000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>4.8843629999999996</v>
+      </c>
+      <c r="C17">
+        <v>3.914069</v>
+      </c>
+      <c r="D17">
+        <v>3.8328720000000001</v>
+      </c>
+      <c r="E17">
+        <v>4.9777940000000003</v>
+      </c>
+      <c r="F17">
+        <v>3.6520049999999999</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>4.2522205999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>8.5</v>
+      </c>
+      <c r="B18">
+        <v>4.9977369999999999</v>
+      </c>
+      <c r="C18">
+        <v>3.8973580000000001</v>
+      </c>
+      <c r="D18">
+        <v>3.9477799999999998</v>
+      </c>
+      <c r="E18">
+        <v>4.950793</v>
+      </c>
+      <c r="F18">
+        <v>3.4057979999999999</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>4.2398932</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>5.0227089999999999</v>
+      </c>
+      <c r="C19">
+        <v>3.9113349999999998</v>
+      </c>
+      <c r="D19">
+        <v>4.0621200000000002</v>
+      </c>
+      <c r="E19">
+        <v>4.9141690000000002</v>
+      </c>
+      <c r="F19">
+        <v>3.7399930000000001</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>4.3300651999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>9.5</v>
+      </c>
+      <c r="B20">
+        <v>4.9984650000000004</v>
+      </c>
+      <c r="C20">
+        <v>4.0014570000000003</v>
+      </c>
+      <c r="D20">
+        <v>4.1070159999999998</v>
+      </c>
+      <c r="E20">
+        <v>4.7296389999999997</v>
+      </c>
+      <c r="F20">
+        <v>4.1575829999999998</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>4.3988320000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>4.9975459999999998</v>
+      </c>
+      <c r="C21">
+        <v>4.1153829999999996</v>
+      </c>
+      <c r="D21">
+        <v>4.3325680000000002</v>
+      </c>
+      <c r="E21">
+        <v>4.8682460000000001</v>
+      </c>
+      <c r="F21">
+        <v>4.5256860000000003</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>4.5678858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>10.5</v>
+      </c>
+      <c r="B22">
+        <v>4.9034040000000001</v>
+      </c>
+      <c r="C22">
+        <v>4.1753429999999998</v>
+      </c>
+      <c r="D22">
+        <v>4.2093170000000004</v>
+      </c>
+      <c r="E22">
+        <v>4.9768470000000002</v>
+      </c>
+      <c r="F22">
+        <v>4.8281539999999996</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>4.6186130000000007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>4.9762630000000003</v>
+      </c>
+      <c r="C23">
+        <v>4.1119079999999997</v>
+      </c>
+      <c r="D23">
+        <v>4.2498060000000004</v>
+      </c>
+      <c r="E23">
+        <v>5.2098139999999997</v>
+      </c>
+      <c r="F23">
+        <v>5.1623419999999998</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>4.7420265999999991</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>11.5</v>
+      </c>
+      <c r="B24">
+        <v>4.8079429999999999</v>
+      </c>
+      <c r="C24">
+        <v>3.8383949999999998</v>
+      </c>
+      <c r="D24">
+        <v>4.6026210000000001</v>
+      </c>
+      <c r="E24">
+        <v>5.4159329999999999</v>
+      </c>
+      <c r="F24">
+        <v>5.2924199999999999</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>4.7914623999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>4.9088609999999999</v>
+      </c>
+      <c r="C25">
+        <v>3.7159149999999999</v>
+      </c>
+      <c r="D25">
+        <v>4.7334889999999996</v>
+      </c>
+      <c r="E25">
+        <v>5.5237780000000001</v>
+      </c>
+      <c r="F25">
+        <v>5.3253079999999997</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>4.8414701999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>12.5</v>
+      </c>
+      <c r="B26">
+        <v>5.1218190000000003</v>
+      </c>
+      <c r="C26">
+        <v>4.1032289999999998</v>
+      </c>
+      <c r="D26">
+        <v>4.4966410000000003</v>
+      </c>
+      <c r="E26">
+        <v>5.5050470000000002</v>
+      </c>
+      <c r="F26">
+        <v>6.2670659999999998</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>5.0987604000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>